--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_generic_tips/lang_generic_tips__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_generic_tips/lang_generic_tips__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch trong {0} giây.</t>
+          <t>Tiêu diệt tất cả kẻ địch trong vòng {0} giây.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Complete Time {0}</t>
+          <t>Thời Gian Hoàn Thành {0}</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Exit sau {0} giây</t>
+          <t>Thoát trong {0} giây</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Phụ</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hoàn thành</t>
+          <t>Nhiệm Vụ Hoàn Thành</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Countdown</t>
+          <t>Đếm Ngược</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Không thể mở bản đồ</t>
+          <t>Không thể mở Bản đồ</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nổi cơn thịnh nộ không ngừng……</t>
+          <t>Thịnh nộ không ngừng……</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Mục tiêu phòng thủ HP 100%</t>
+          <t>HP mục tiêu bảo vệ: 100%</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Hiện tại: 0/100</t>
+          <t>Hiện Tại: 0/100</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Nhân vật Thử nghiệm</t>
+          <t>Nhân vật thử nghiệm</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả hướng dẫn để hoàn tất Trial</t>
+          <t>Hoàn thành tất cả hướng dẫn để vượt qua Thử Thách</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Hoàn Tất Healing</t>
+          <t>Đã hồi phục hoàn toàn</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch trong vòng 600 giây</t>
+          <t>Tiêu diệt tất cả kẻ địch trong vòng 600 giây.</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Nổi cơn thịnh nộ không ngừng……</t>
+          <t>Thịnh nộ không ngừng……</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>HP phục hồi</t>
+          <t>HP đã hồi phục</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Hãy đánh bại tất cả kẻ địch trong vòng 300 giây.</t>
+          <t>Tiêu diệt tất cả kẻ địch trong vòng 300 giây.</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point Tầng 1</t>
+          <t>Trạm Nghiên cứu Zero Point - Tầng 1</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch</t>
+          <t>Tiêu diệt tất cả kẻ địch</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point Tầng 2</t>
+          <t>Trạm Nghiên cứu Điểm Không F2</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch</t>
+          <t>Tiêu diệt tất cả kẻ địch</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F3</t>
+          <t>Trạm Nghiên cứu Điểm Không F3</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Increase ATK của kẻ địch thêm 10%, tối đa 50%, sau mỗi lần trúng mục tiêu.</t>
+          <t>Tăng 10% ATK của kẻ địch sau mỗi lần trúng mục tiêu, tối đa 50%.</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F4</t>
+          <t>Trạm Nghiên cứu Điểm Không F4</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Increase ATK của kẻ địch thêm 10%, tối đa 50%, sau mỗi lần trúng mục tiêu.</t>
+          <t>Tăng 10% ATK của kẻ địch sau mỗi lần trúng mục tiêu, tối đa 50%.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F5</t>
+          <t>Trạm Nghiên cứu Điểm Không F5</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Kẻ địch phục hồi 3.5% HP tối đa mỗi 5 giây.</t>
+          <t>Kẻ địch hồi phục 3.5% HP tối đa mỗi 5 giây.</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F6</t>
+          <t>Trạm Nghiên cứu Điểm Không F6</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Kẻ địch phục hồi 3.5% HP tối đa mỗi 5 giây.</t>
+          <t>Kẻ địch hồi phục 3.5% HP tối đa mỗi 5 giây.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F7</t>
+          <t>Trạm Nghiên cứu Điểm Không F7</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Resonator trong trận sẽ mất 1.5% HP tối đa mỗi giây.</t>
+          <t>Nhân vật trên chiến trường sẽ mất 1,5% HP tối đa mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F8</t>
+          <t>Trạm Nghiên cứu Điểm Không F8</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Resonator trong trận sẽ mất 1.5% HP tối đa mỗi giây.</t>
+          <t>Nhân vật trên chiến trường sẽ mất 1,5% HP tối đa mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Trạm Nghiên cứu Zero Point F9</t>
+          <t>Trạm Nghiên cứu Điểm Không F9</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Increase 50% ATK của kẻ địch. Increase Tốc Độ Phục Hồi STA của đội.</t>
+          <t>Tăng 50% ATK của kẻ địch. Tăng Tốc Độ Hồi Phục Thể Lực của đội.</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Ambience</t>
+          <t>Bầu không khí</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Tương tác với Dây Âm để kích hoạt Bối Cảnh</t>
+          <t>Tương tác với Chuỗi Âm để kích hoạt Bối Cảnh</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Increase 10% ATK của kẻ địch sau mỗi lần trúng mục tiêu.</t>
+          <t>Tăng 10% ATK của kẻ địch sau mỗi lần trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Kẻ địch phục hồi 3.5% HP tối đa mỗi 5 giây.</t>
+          <t>Kẻ địch hồi phục 3.5% HP tối đa mỗi 5 giây.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Resonator trong trận sẽ mất 1.5% HP tối đa mỗi giây.</t>
+          <t>Nhân vật trên chiến trường sẽ mất 1,5% HP tối đa mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Increase 50% ATK của kẻ địch. Increase Tốc Độ Phục Hồi STA của đội.</t>
+          <t>Tăng 50% ATK của kẻ địch. Tăng Tốc Độ Hồi Phục Thể Lực của đội.</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Hoàn thành Challenge. Bạn có thể rời khỏi bằng cách tương tác với lối ra.</t>
+          <t>Hoàn thành Thử thách. Tương tác với lối ra để rời khỏi.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Bạn có thể sử dụng Crystallized Plate để đổi lấy phần thưởng, sau đó tương tác với lối ra để rời đi.</t>
+          <t>Bạn có thể dùng Tấm Kết Tinh để đổi phần thưởng, sau đó tương tác với lối ra để rời đi.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Đã mở khóa tệp mới</t>
+          <t>Tệp mới đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hoàn thành nhiều lượt luyện bắn trong thời gian giới hạn.</t>
+          <t>Hoàn thành nhiều lượt bắn trong thời gian giới hạn.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử thách lần đầu</t>
+          <t>Hoàn Thành Thử Thách Lần Đầu</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Mail đã xóa</t>
+          <t>Thư đã xóa</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Claimed thưởng</t>
+          <t>Đã Nhận Phần Thưởng</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Đã thu hồi thư</t>
+          <t>Thư đã thu hồi</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Không thể nhận thưởng từ thư đã hết hạn.</t>
+          <t>Không thể nhận phần thưởng từ thư đã hết hạn.</t>
         </is>
       </c>
     </row>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ</t>
+          <t>Nhiệm Vụ Hoàn Thành</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Đến Pioneer Association để nhận thưởng.</t>
+          <t>Hãy đến Hiệp Hội Tiên Phong để nhận thưởng</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Chặng phụ bị khóa</t>
+          <t>Né Tránh Bên Bị Khóa</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Vui lòng đọc và nhấn đồng ý với thỏa thuận sau trước khi bắt đầu trò chơi.</t>
+          <t>Vui lòng đọc và nhấp đồng ý với thỏa thuận dưới đây trước khi bắt đầu trò chơi.</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Rover này đang trong Danh sách Bạn bè của bạn</t>
+          <t>Vận Mệnh Giả này đang trong danh sách Bạn Bè của bạn.</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Rover này không có trong danh sách Bạn bè của bạn.</t>
+          <t>Vận Mệnh Giả này không có trong danh sách Bạn Bè của bạn.</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Không tìm thấy hồ sơ đăng ký.</t>
+          <t>Không tìm thấy hồ sơ ứng dụng.</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5319,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Danh sách bạn bè đã đầy</t>
+          <t>Danh sách bạn bè của bạn đã đầy</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Danh sách bạn bè của Rover này đã đầy.</t>
+          <t>Danh sách bạn bè của Vận Mệnh Giả này đã đầy.</t>
         </is>
       </c>
     </row>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Rover này đang trong Danh Sách Chặn của bạn</t>
+          <t>Vận Mệnh Giả này đang trong danh sách chặn của bạn</t>
         </is>
       </c>
     </row>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Rover này không có trong Blocklist của bạn</t>
+          <t>Vận Mệnh Giả này không có trong danh sách Chặn của bạn.</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Blocklist đã đầy</t>
+          <t>Danh sách chặn đã đầy</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Bạn đã được thêm vào danh sách chặn của Rover này.</t>
+          <t>Bạn đã bị thêm vào danh sách chặn của Vận Mệnh Giả này.</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Bạn không thể tìm chính mình.</t>
+          <t>Bạn không thể tìm kiếm chính mình.</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5839,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Rover này đang trong danh sách Lời Mời Kết Bạn của bạn.</t>
+          <t>Vận Mệnh Giả này đang trong danh sách Yêu Cầu Kết Bạn của bạn.</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Đã sao chép UID vào bộ nhớ tạm.</t>
+          <t>UID đã được sao chép vào bộ nhớ tạm.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Bạn đã thêm {0} vào danh sách chặn</t>
+          <t>Bạn đã thêm {0} vào danh sách chặn.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Bạn đã xóa {0} khỏi danh sách chặn</t>
+          <t>Bạn đã xóa {0} khỏi danh sách chặn.</t>
         </is>
       </c>
     </row>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Bạn đã đạt giới hạn đăng ký hàng ngày</t>
+          <t>Bạn đã đạt giới hạn số lần đăng ký hàng ngày.</t>
         </is>
       </c>
     </row>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Bạn đã gửi yêu cầu trước đó</t>
+          <t>Bạn đã gửi đơn đăng ký trước đó rồi.</t>
         </is>
       </c>
     </row>
@@ -6229,7 +6229,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Rover này đã xóa bạn khỏi danh sách Bạn bè</t>
+          <t>Vận Mệnh Giả này đã xóa bạn khỏi danh sách bạn bè.</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Vui lòng chọn ô lưới bên trái.</t>
+          <t>Vui lòng chọn ô ở bên trái.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Saved</t>
+          <t>Đã Lưu</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Nhân vật thử nghiệm không thể dịch chuyển</t>
+          <t>Không thể dịch chuyển nhân vật thử nghiệm</t>
         </is>
       </c>
     </row>
@@ -6684,7 +6684,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Nhân vật Trial không thể tham gia co-op.</t>
+          <t>Nhân vật thử nghiệm không thể tham gia chế độ cộng tác.</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Không thể đặt nhân vật thử nghiệm vào đội</t>
+          <t>Không thể đặt nhân vật thử nghiệm vào đội hình</t>
         </is>
       </c>
     </row>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ.</t>
+          <t>Vật liệu không đủ</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Kinh nghiệm đã đạt tối đa</t>
+          <t>Kinh Nghiệm Đạt Tối Đa</t>
         </is>
       </c>
     </row>
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ.</t>
+          <t>Vật liệu không đủ</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Vui lòng cho nguyên liệu vào</t>
+          <t>Vui lòng đặt nguyên liệu vào</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng yêu cầu nâng cấp.</t>
+          <t>Yêu cầu nâng cấp chưa hoàn tất.</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7399,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Result sẽ có hiệu lực vào ngày tiếp theo</t>
+          <t>Kết quả sẽ có hiệu lực vào ngày hôm sau</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Hằng ngày</t>
+          <t>Nhiệm Vụ Hằng Ngày Hoàn Thành</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Bạn có thể đổi thưởng ngay bây giờ.</t>
+          <t>Bạn có thể đổi phần thưởng ngay bây giờ.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Đã xác định mục tiêu dò tìm</t>
+          <t>Đã xác định mục tiêu thăm dò</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Mở khóa Tacet Field</t>
+          <t>Tổ Tacet đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Mở khóa Tacet Field</t>
+          <t>Tổ Tacet đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng điều kiện mở khóa</t>
+          <t>Chưa hoàn thành điều kiện mở khóa</t>
         </is>
       </c>
     </row>
@@ -7919,7 +7919,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Đừng vội lao vào khu vực chưa biết lúc này.</t>
+          <t>Đừng vội lao vào những khu vực chưa rõ tình hình.</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Không thể đặt thêm nhân vật hoạt động.</t>
+          <t>Không thể đặt thêm Cộng Hưởng Giả hoạt động.</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Bạn cần xếp ít nhất một nhân vật vào đội</t>
+          <t>Bạn cần đặt ít nhất một Cộng Hưởng Giả vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Rover này đang ngoại tuyến hoặc UID không chính xác</t>
+          <t>Vận Mệnh Giả này đang ngoại tuyến hoặc UID không chính xác.</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Character Locked {0}</t>
+          <t>Đã khóa nhân vật {0}</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Bạn đã thành thạo chế tác {0}.</t>
+          <t>Bạn đã thành thạo chế tạo {0}.</t>
         </is>
       </c>
     </row>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Chưa đáp ứng yêu cầu nâng cấp.</t>
+          <t>Yêu cầu nâng cấp chưa hoàn tất.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Star Align chưa mở</t>
+          <t>Sao Đồng Điệu chưa mở</t>
         </is>
       </c>
     </row>
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Không thể mua vật phẩm Star Align hiện tại</t>
+          <t>Không thể mua vật phẩm Sắp Hàng Sao hiện tại</t>
         </is>
       </c>
     </row>
@@ -8634,7 +8634,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Không thể thanh toán trong bài test này, không thể mua hàng.</t>
+          <t>Giao dịch không khả dụng trong bản thử nghiệm này, không thể mua hàng.</t>
         </is>
       </c>
     </row>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Vui lòng nhập tại đây</t>
+          <t>Hãy nhập vào đây</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Bạn không thể đặt Reverberation trong Chế độ Đồng đội</t>
+          <t>Bạn không thể đặt Reverberation trong Chế độ Hợp Tác</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Liked</t>
+          <t>Đã thích</t>
         </is>
       </c>
     </row>
@@ -9219,7 +9219,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Disliked</t>
+          <t>Không ưa thích</t>
         </is>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Bạn không thể chụp ảnh ở trạng thái hiện tại.</t>
+          <t>Hiện tại bạn không thể chụp ảnh.</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9349,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Ảnh đã lưu vào thư mục /{0}</t>
+          <t>Ảnh đã được lưu vào thư mục /{0}</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch trong {0} giây.</t>
+          <t>Tiêu diệt tất cả kẻ địch trong vòng {0} giây.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Complete Time {0}</t>
+          <t>Thời Gian Hoàn Thành {0}</t>
         </is>
       </c>
     </row>
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Exit sau {0} giây</t>
+          <t>Thoát trong {0} giây</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9609,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Thử thách thất bại</t>
+          <t>Thử thách Thất bại</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Phụ</t>
+          <t>Nhiệm Vụ Phụ</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Nhiệm vụ hoàn thành</t>
+          <t>Nhiệm Vụ Hoàn Thành</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Countdown</t>
+          <t>Đếm Ngược</t>
         </is>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Từ thông dụng</t>
+          <t>Từ ngữ thông dụng</t>
         </is>
       </c>
     </row>
@@ -10194,7 +10194,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Act X - Hồi X $[begin]</t>
+          <t>Chương X - Hồi X $[Bắt đầu]</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Act X - Hồi X $[Kết]</t>
+          <t>Chương X - Hồi X $[Kết thúc]</t>
         </is>
       </c>
     </row>
@@ -10389,7 +10389,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ</t>
+          <t>Nhiệm Vụ Hoàn Thành</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Đến Pioneer Association để nhận thưởng.</t>
+          <t>Hãy đến Hiệp Hội Tiên Phong để nhận thưởng</t>
         </is>
       </c>
     </row>
